--- a/Specialty Claims Pending 2026-S1.xlsx
+++ b/Specialty Claims Pending 2026-S1.xlsx
@@ -33,7 +33,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,11 @@
         <fgColor rgb="FF7F6000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -63,13 +68,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,7 +467,7 @@
     <col width="22" customWidth="1" min="25" max="25"/>
     <col width="19" customWidth="1" min="26" max="26"/>
     <col width="24" customWidth="1" min="27" max="27"/>
-    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="70" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -14892,7 +14901,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr">
+      <c r="J151" s="3" t="inlineStr">
         <is>
           <t>Finalized</t>
         </is>
@@ -14945,7 +14954,7 @@
       <c r="AA151" t="n">
         <v>116</v>
       </c>
-      <c r="AB151" t="inlineStr">
+      <c r="AB151" s="4" t="inlineStr">
         <is>
           <t>Adjusted - CPT 93923 bundles with 93925 and 93970 - 93923 billed on claim 568254615</t>
         </is>
@@ -19704,7 +19713,7 @@
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="J201" t="inlineStr">
+      <c r="J201" s="3" t="inlineStr">
         <is>
           <t>Denied</t>
         </is>
@@ -19757,7 +19766,7 @@
       <c r="AA201" t="n">
         <v>80</v>
       </c>
-      <c r="AB201" t="inlineStr">
+      <c r="AB201" s="4" t="inlineStr">
         <is>
           <t>Corrected service line 1 - Changed to 99492, and resubmitted - Processed date 06/10/2026</t>
         </is>
@@ -20551,7 +20560,7 @@
           <t>Molina Complete Care of Arizona (Magellan Complete Care AZ)</t>
         </is>
       </c>
-      <c r="J210" t="inlineStr">
+      <c r="J210" s="3" t="inlineStr">
         <is>
           <t>Finalized</t>
         </is>
@@ -20609,7 +20618,7 @@
       <c r="AA210" t="n">
         <v>79</v>
       </c>
-      <c r="AB210" t="inlineStr">
+      <c r="AB210" s="4" t="inlineStr">
         <is>
           <t>Billed PT according to ABN charges agreed.</t>
         </is>
@@ -21104,7 +21113,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J216" t="inlineStr">
+      <c r="J216" s="3" t="inlineStr">
         <is>
           <t>Denied</t>
         </is>
@@ -21157,7 +21166,7 @@
       <c r="AA216" t="n">
         <v>88</v>
       </c>
-      <c r="AB216" t="inlineStr">
+      <c r="AB216" s="4" t="inlineStr">
         <is>
           <t>DMinker30A corrected claim and resubmitted</t>
         </is>
@@ -21202,7 +21211,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J217" t="inlineStr">
+      <c r="J217" s="3" t="inlineStr">
         <is>
           <t>Denied</t>
         </is>
@@ -21255,7 +21264,7 @@
       <c r="AA217" t="n">
         <v>88</v>
       </c>
-      <c r="AB217" t="inlineStr">
+      <c r="AB217" s="4" t="inlineStr">
         <is>
           <t>DMinker30A corrected claim and resubmitted</t>
         </is>
@@ -29442,7 +29451,7 @@
           <t>Arizona Complete Health (Centene)</t>
         </is>
       </c>
-      <c r="J308" t="inlineStr">
+      <c r="J308" s="3" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -29485,7 +29494,7 @@
       <c r="AA308" t="n">
         <v>89</v>
       </c>
-      <c r="AB308" t="inlineStr">
+      <c r="AB308" s="4" t="inlineStr">
         <is>
           <t>On hold - Missing MR - Uploaded MR on portal</t>
         </is>
@@ -35446,7 +35455,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J373" t="inlineStr">
+      <c r="J373" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
@@ -35509,7 +35518,7 @@
       <c r="AA373" t="n">
         <v>87</v>
       </c>
-      <c r="AB373" t="inlineStr">
+      <c r="AB373" s="4" t="inlineStr">
         <is>
           <t>Removed 20936, and resubmited</t>
         </is>
@@ -36276,7 +36285,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J383" t="inlineStr">
+      <c r="J383" s="3" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -36319,7 +36328,7 @@
       <c r="AA383" t="n">
         <v>79</v>
       </c>
-      <c r="AB383" t="inlineStr">
+      <c r="AB383" s="4" t="inlineStr">
         <is>
           <t>Waiting for Juan to send the ultrasounds to me</t>
         </is>
@@ -36364,7 +36373,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J384" t="inlineStr">
+      <c r="J384" s="3" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -36407,7 +36416,7 @@
       <c r="AA384" t="n">
         <v>79</v>
       </c>
-      <c r="AB384" t="inlineStr">
+      <c r="AB384" s="4" t="inlineStr">
         <is>
           <t>Waiting for Juan to send the ultrasounds to me</t>
         </is>
@@ -36452,7 +36461,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J385" t="inlineStr">
+      <c r="J385" s="3" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -36495,7 +36504,7 @@
       <c r="AA385" t="n">
         <v>79</v>
       </c>
-      <c r="AB385" t="inlineStr">
+      <c r="AB385" s="4" t="inlineStr">
         <is>
           <t>Waiting for Juan to send the ultrasounds to me</t>
         </is>
@@ -37201,7 +37210,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J393" t="inlineStr">
+      <c r="J393" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
@@ -37259,7 +37268,7 @@
       <c r="AA393" t="n">
         <v>87</v>
       </c>
-      <c r="AB393" t="inlineStr">
+      <c r="AB393" s="4" t="inlineStr">
         <is>
           <t>Removed 20936, and resubmited</t>
         </is>
@@ -37304,7 +37313,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J394" t="inlineStr">
+      <c r="J394" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
@@ -37362,7 +37371,7 @@
       <c r="AA394" t="n">
         <v>87</v>
       </c>
-      <c r="AB394" t="inlineStr">
+      <c r="AB394" s="4" t="inlineStr">
         <is>
           <t>Removed 20936, and resubmited</t>
         </is>
@@ -37407,7 +37416,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J395" t="inlineStr">
+      <c r="J395" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
@@ -37470,7 +37479,7 @@
       <c r="AA395" t="n">
         <v>87</v>
       </c>
-      <c r="AB395" t="inlineStr">
+      <c r="AB395" s="4" t="inlineStr">
         <is>
           <t>Removed 20936, and resubmited</t>
         </is>
@@ -52086,7 +52095,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J556" t="inlineStr">
+      <c r="J556" s="3" t="inlineStr">
         <is>
           <t>Denied</t>
         </is>
@@ -52144,7 +52153,7 @@
       <c r="AA556" t="n">
         <v>87</v>
       </c>
-      <c r="AB556" t="inlineStr">
+      <c r="AB556" s="4" t="inlineStr">
         <is>
           <t>Uploaded MR - PIQ-88944138 - Processed Date 05/28/2026</t>
         </is>
@@ -52189,7 +52198,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J557" t="inlineStr">
+      <c r="J557" s="3" t="inlineStr">
         <is>
           <t>Denied</t>
         </is>
@@ -52247,7 +52256,7 @@
       <c r="AA557" t="n">
         <v>87</v>
       </c>
-      <c r="AB557" t="inlineStr">
+      <c r="AB557" s="4" t="inlineStr">
         <is>
           <t>Uploaded MR - PIQ-88944138 - Processed Date 05/28/2026</t>
         </is>
@@ -52292,7 +52301,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J558" t="inlineStr">
+      <c r="J558" s="3" t="inlineStr">
         <is>
           <t>Denied</t>
         </is>
@@ -52350,7 +52359,7 @@
       <c r="AA558" t="n">
         <v>87</v>
       </c>
-      <c r="AB558" t="inlineStr">
+      <c r="AB558" s="4" t="inlineStr">
         <is>
           <t>Uploaded MR - PIQ-88944138 - Processed Date 05/28/2026</t>
         </is>
@@ -54042,7 +54051,7 @@
           <t>Mercy Care RBHA</t>
         </is>
       </c>
-      <c r="J578" t="inlineStr">
+      <c r="J578" s="3" t="inlineStr">
         <is>
           <t>Denied</t>
         </is>
@@ -54095,7 +54104,7 @@
       <c r="AA578" t="n">
         <v>78</v>
       </c>
-      <c r="AB578" t="inlineStr">
+      <c r="AB578" s="4" t="inlineStr">
         <is>
           <t>UHC not active on DOS - Resubmitted to Mercy Care (secondary) - Processed date 06/10/2026</t>
         </is>
@@ -54140,7 +54149,7 @@
           <t>Mercy Care RBHA</t>
         </is>
       </c>
-      <c r="J579" t="inlineStr">
+      <c r="J579" s="3" t="inlineStr">
         <is>
           <t>Denied</t>
         </is>
@@ -54193,7 +54202,7 @@
       <c r="AA579" t="n">
         <v>78</v>
       </c>
-      <c r="AB579" t="inlineStr">
+      <c r="AB579" s="4" t="inlineStr">
         <is>
           <t>UHC not active on DOS - Resubmitted to Mercy Care (secondary) - Processed date 06/10/2026</t>
         </is>
@@ -54238,7 +54247,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J580" t="inlineStr">
+      <c r="J580" s="3" t="inlineStr">
         <is>
           <t>Denied</t>
         </is>
@@ -54301,7 +54310,7 @@
       <c r="AA580" t="n">
         <v>79</v>
       </c>
-      <c r="AB580" t="inlineStr">
+      <c r="AB580" s="4" t="inlineStr">
         <is>
           <t>Uploaded MR - PIQ-88975230 - Processed date 08/08/2026</t>
         </is>
@@ -54718,7 +54727,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J585" t="inlineStr">
+      <c r="J585" s="3" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
@@ -54771,7 +54780,7 @@
       <c r="AA585" t="n">
         <v>79</v>
       </c>
-      <c r="AB585" t="inlineStr">
+      <c r="AB585" s="4" t="inlineStr">
         <is>
           <t>Pending posting</t>
         </is>
@@ -54816,7 +54825,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J586" t="inlineStr">
+      <c r="J586" s="3" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
@@ -54869,7 +54878,7 @@
       <c r="AA586" t="n">
         <v>79</v>
       </c>
-      <c r="AB586" t="inlineStr">
+      <c r="AB586" s="4" t="inlineStr">
         <is>
           <t>Pending posting</t>
         </is>
@@ -54914,7 +54923,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J587" t="inlineStr">
+      <c r="J587" s="3" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
@@ -54967,7 +54976,7 @@
       <c r="AA587" t="n">
         <v>79</v>
       </c>
-      <c r="AB587" t="inlineStr">
+      <c r="AB587" s="4" t="inlineStr">
         <is>
           <t>Pending posting</t>
         </is>
@@ -63309,7 +63318,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J682" t="inlineStr">
+      <c r="J682" s="3" t="inlineStr">
         <is>
           <t>Denied</t>
         </is>
@@ -63362,7 +63371,7 @@
       <c r="AA682" t="n">
         <v>82</v>
       </c>
-      <c r="AB682" t="inlineStr">
+      <c r="AB682" s="4" t="inlineStr">
         <is>
           <t>Checking with auth team</t>
         </is>
@@ -64938,7 +64947,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J700" t="inlineStr">
+      <c r="J700" s="3" t="inlineStr">
         <is>
           <t>Denied</t>
         </is>
@@ -64986,7 +64995,7 @@
       <c r="AA700" t="n">
         <v>86</v>
       </c>
-      <c r="AB700" t="inlineStr">
+      <c r="AB700" s="4" t="inlineStr">
         <is>
           <t>Resubmitted with 63030+63035</t>
         </is>
@@ -65031,7 +65040,7 @@
           <t>LIEN 03</t>
         </is>
       </c>
-      <c r="J701" t="inlineStr">
+      <c r="J701" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
@@ -65094,7 +65103,7 @@
       <c r="AA701" t="n">
         <v>85</v>
       </c>
-      <c r="AB701" t="inlineStr">
+      <c r="AB701" s="4" t="inlineStr">
         <is>
           <t>Remove CPT A6219, and resubmitted</t>
         </is>
@@ -67150,7 +67159,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J724" t="inlineStr">
+      <c r="J724" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
@@ -67203,7 +67212,7 @@
       <c r="AA724" t="n">
         <v>82</v>
       </c>
-      <c r="AB724" t="inlineStr">
+      <c r="AB724" s="4" t="inlineStr">
         <is>
           <t>Waiting for Bri's reply on how to get WCEOB</t>
         </is>
@@ -67248,7 +67257,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J725" t="inlineStr">
+      <c r="J725" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
@@ -67301,7 +67310,7 @@
       <c r="AA725" t="n">
         <v>82</v>
       </c>
-      <c r="AB725" t="inlineStr">
+      <c r="AB725" s="4" t="inlineStr">
         <is>
           <t>Waiting for Bri's reply on how to get WCEOB</t>
         </is>
@@ -68158,7 +68167,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J735" t="inlineStr">
+      <c r="J735" s="3" t="inlineStr">
         <is>
           <t>Finalized</t>
         </is>
@@ -68216,7 +68225,7 @@
       <c r="AA735" t="n">
         <v>78</v>
       </c>
-      <c r="AB735" t="inlineStr">
+      <c r="AB735" s="4" t="inlineStr">
         <is>
           <t>No auth on file - Adjusted</t>
         </is>
@@ -68970,7 +68979,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J744" t="inlineStr">
+      <c r="J744" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
@@ -69023,7 +69032,7 @@
       <c r="AA744" t="n">
         <v>80</v>
       </c>
-      <c r="AB744" t="inlineStr">
+      <c r="AB744" s="4" t="inlineStr">
         <is>
           <t>Corrected service line 1 to 99492, and resubmitted - Processed date 06/16/2026</t>
         </is>
@@ -69068,7 +69077,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J745" t="inlineStr">
+      <c r="J745" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
@@ -69121,7 +69130,7 @@
       <c r="AA745" t="n">
         <v>80</v>
       </c>
-      <c r="AB745" t="inlineStr">
+      <c r="AB745" s="4" t="inlineStr">
         <is>
           <t>Corrected service line 1 to 99492, and resubmitted - Processed date 06/16/2026</t>
         </is>
@@ -69166,7 +69175,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J746" t="inlineStr">
+      <c r="J746" s="3" t="inlineStr">
         <is>
           <t>Denied</t>
         </is>
@@ -69214,7 +69223,7 @@
       <c r="AA746" t="n">
         <v>79</v>
       </c>
-      <c r="AB746" t="inlineStr">
+      <c r="AB746" s="4" t="inlineStr">
         <is>
           <t>Checking with biller</t>
         </is>
@@ -69259,7 +69268,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J747" t="inlineStr">
+      <c r="J747" s="3" t="inlineStr">
         <is>
           <t>Denied</t>
         </is>
@@ -69307,7 +69316,7 @@
       <c r="AA747" t="n">
         <v>79</v>
       </c>
-      <c r="AB747" t="inlineStr">
+      <c r="AB747" s="4" t="inlineStr">
         <is>
           <t>Checking with biller</t>
         </is>
@@ -74460,7 +74469,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J804" t="inlineStr">
+      <c r="J804" s="3" t="inlineStr">
         <is>
           <t>Denied</t>
         </is>
@@ -74518,7 +74527,7 @@
       <c r="AA804" t="n">
         <v>82</v>
       </c>
-      <c r="AB804" t="inlineStr">
+      <c r="AB804" s="4" t="inlineStr">
         <is>
           <t>Removed rendering, added servicing, changed from professional to DME, and resubmitted - Denied due to missing auth - I see rendering OON -  Processed date 06/12/2026</t>
         </is>
@@ -74827,7 +74836,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J808" t="inlineStr">
+      <c r="J808" s="3" t="inlineStr">
         <is>
           <t>Finalized</t>
         </is>
@@ -74885,7 +74894,7 @@
       <c r="AA808" t="n">
         <v>85</v>
       </c>
-      <c r="AB808" t="inlineStr">
+      <c r="AB808" s="4" t="inlineStr">
         <is>
           <t>Auth only included 63650 - Adjusted 63685</t>
         </is>
@@ -76313,7 +76322,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J825" t="inlineStr">
+      <c r="J825" s="3" t="inlineStr">
         <is>
           <t>Denied</t>
         </is>
@@ -76376,7 +76385,7 @@
       <c r="AA825" t="n">
         <v>58</v>
       </c>
-      <c r="AB825" t="inlineStr">
+      <c r="AB825" s="4" t="inlineStr">
         <is>
           <t>Delete 93923 that's bundling, and resubmitted -  93923 billed on claim 568263929 - Processed Date 06/25/2026</t>
         </is>
@@ -76421,7 +76430,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J826" t="inlineStr">
+      <c r="J826" s="3" t="inlineStr">
         <is>
           <t>Denied</t>
         </is>
@@ -76484,7 +76493,7 @@
       <c r="AA826" t="n">
         <v>58</v>
       </c>
-      <c r="AB826" t="inlineStr">
+      <c r="AB826" s="4" t="inlineStr">
         <is>
           <t>Delete 93923 that's bundling, and resubmitted -  93923 billed on claim 568263929 - Processed Date 06/25/2026</t>
         </is>
@@ -76529,7 +76538,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J827" t="inlineStr">
+      <c r="J827" s="3" t="inlineStr">
         <is>
           <t>Denied</t>
         </is>
@@ -76592,7 +76601,7 @@
       <c r="AA827" t="n">
         <v>58</v>
       </c>
-      <c r="AB827" t="inlineStr">
+      <c r="AB827" s="4" t="inlineStr">
         <is>
           <t>Delete 93923 that's bundling, and resubmitted -  93923 billed on claim 568263929 - Processed Date 06/25/2026</t>
         </is>
@@ -79996,7 +80005,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J866" t="inlineStr">
+      <c r="J866" s="3" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
@@ -80039,7 +80048,7 @@
       <c r="AA866" t="n">
         <v>52</v>
       </c>
-      <c r="AB866" t="inlineStr">
+      <c r="AB866" s="4" t="inlineStr">
         <is>
           <t>Pending posting</t>
         </is>
@@ -80084,7 +80093,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J867" t="inlineStr">
+      <c r="J867" s="3" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
@@ -80127,7 +80136,7 @@
       <c r="AA867" t="n">
         <v>52</v>
       </c>
-      <c r="AB867" t="inlineStr">
+      <c r="AB867" s="4" t="inlineStr">
         <is>
           <t>Pending posting</t>
         </is>
@@ -80436,7 +80445,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J871" t="inlineStr">
+      <c r="J871" s="3" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -80479,7 +80488,7 @@
       <c r="AA871" t="n">
         <v>86</v>
       </c>
-      <c r="AB871" t="inlineStr">
+      <c r="AB871" s="4" t="inlineStr">
         <is>
           <t>Uploaded MR - PIQ-88903761</t>
         </is>
@@ -81268,7 +81277,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J880" t="inlineStr">
+      <c r="J880" s="3" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -81311,7 +81320,7 @@
       <c r="AA880" t="n">
         <v>86</v>
       </c>
-      <c r="AB880" t="inlineStr">
+      <c r="AB880" s="4" t="inlineStr">
         <is>
           <t>Uploaded MR - PIQ-88903761</t>
         </is>
@@ -82151,7 +82160,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J891" t="inlineStr">
+      <c r="J891" s="3" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -82194,7 +82203,7 @@
       <c r="AA891" t="n">
         <v>78</v>
       </c>
-      <c r="AB891" t="inlineStr">
+      <c r="AB891" s="4" t="inlineStr">
         <is>
           <t>Uploaded MR - PIQ-88958247</t>
         </is>
@@ -86387,7 +86396,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J938" t="inlineStr">
+      <c r="J938" s="3" t="inlineStr">
         <is>
           <t>Finalized</t>
         </is>
@@ -86435,7 +86444,7 @@
       <c r="AA938" t="n">
         <v>88</v>
       </c>
-      <c r="AB938" t="inlineStr">
+      <c r="AB938" s="4" t="inlineStr">
         <is>
           <t>PR amount assigned as per EOB and adjusted</t>
         </is>
@@ -86480,7 +86489,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J939" t="inlineStr">
+      <c r="J939" s="3" t="inlineStr">
         <is>
           <t>Finalized</t>
         </is>
@@ -86528,7 +86537,7 @@
       <c r="AA939" t="n">
         <v>88</v>
       </c>
-      <c r="AB939" t="inlineStr">
+      <c r="AB939" s="4" t="inlineStr">
         <is>
           <t>PR amount assigned as per EOB and adjusted</t>
         </is>
@@ -92990,7 +92999,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J1014" t="inlineStr">
+      <c r="J1014" s="3" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -93033,7 +93042,7 @@
       <c r="AA1014" t="n">
         <v>78</v>
       </c>
-      <c r="AB1014" t="inlineStr">
+      <c r="AB1014" s="4" t="inlineStr">
         <is>
           <t>Uploaded MR - PIQ-88958247</t>
         </is>
@@ -98376,7 +98385,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J1076" t="inlineStr">
+      <c r="J1076" s="3" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -98419,7 +98428,7 @@
       <c r="AA1076" t="n">
         <v>86</v>
       </c>
-      <c r="AB1076" t="inlineStr">
+      <c r="AB1076" s="4" t="inlineStr">
         <is>
           <t>Uploaded MR - PIQ-88903858</t>
         </is>
@@ -98464,7 +98473,7 @@
           <t>No Payer</t>
         </is>
       </c>
-      <c r="J1077" t="inlineStr">
+      <c r="J1077" s="3" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -98507,7 +98516,7 @@
       <c r="AA1077" t="n">
         <v>86</v>
       </c>
-      <c r="AB1077" t="inlineStr">
+      <c r="AB1077" s="4" t="inlineStr">
         <is>
           <t>Uploaded MR - PIQ-88903858</t>
         </is>
